--- a/data/intermediate/Afu_reduced.xlsx
+++ b/data/intermediate/Afu_reduced.xlsx
@@ -4985,12 +4985,6 @@
       <c r="F2" t="s" s="1">
         <v>20</v>
       </c>
-      <c r="G2" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H2" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K2" t="s" s="1">
         <v>21</v>
       </c>
@@ -5011,12 +5005,6 @@
       <c r="F3" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G3" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H3" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K3" t="s" s="1">
         <v>27</v>
       </c>
@@ -5037,12 +5025,6 @@
       <c r="F4" t="s" s="1">
         <v>32</v>
       </c>
-      <c r="G4" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H4" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K4" t="s" s="1">
         <v>33</v>
       </c>
@@ -5063,12 +5045,6 @@
       <c r="F5" t="s" s="1">
         <v>32</v>
       </c>
-      <c r="G5" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H5" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K5" t="s" s="1">
         <v>33</v>
       </c>
@@ -5089,12 +5065,6 @@
       <c r="F6" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="G6" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H6" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K6" t="s" s="1">
         <v>41</v>
       </c>
@@ -5115,12 +5085,6 @@
       <c r="F7" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="G7" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H7" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K7" t="s" s="1">
         <v>47</v>
       </c>
@@ -5141,12 +5105,6 @@
       <c r="F8" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="G8" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H8" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K8" t="s" s="1">
         <v>53</v>
       </c>
@@ -5167,12 +5125,6 @@
       <c r="F9" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="G9" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H9" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K9" t="s" s="1">
         <v>53</v>
       </c>
@@ -5193,12 +5145,6 @@
       <c r="F10" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="G10" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H10" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K10" t="s" s="1">
         <v>61</v>
       </c>
@@ -5219,12 +5165,6 @@
       <c r="F11" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G11" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H11" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K11" t="s" s="1">
         <v>67</v>
       </c>
@@ -5245,12 +5185,6 @@
       <c r="F12" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G12" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H12" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K12" t="s" s="1">
         <v>67</v>
       </c>
@@ -5271,12 +5205,6 @@
       <c r="F13" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G13" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H13" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K13" t="s" s="1">
         <v>67</v>
       </c>
@@ -5297,12 +5225,6 @@
       <c r="F14" t="s" s="1">
         <v>75</v>
       </c>
-      <c r="G14" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H14" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K14" t="s" s="1">
         <v>76</v>
       </c>
@@ -5323,12 +5245,6 @@
       <c r="F15" t="s" s="1">
         <v>75</v>
       </c>
-      <c r="G15" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H15" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K15" t="s" s="1">
         <v>76</v>
       </c>
@@ -5349,12 +5265,6 @@
       <c r="F16" t="s" s="1">
         <v>75</v>
       </c>
-      <c r="G16" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H16" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K16" t="s" s="1">
         <v>76</v>
       </c>
@@ -5375,12 +5285,6 @@
       <c r="F17" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="G17" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H17" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K17" t="s" s="1">
         <v>82</v>
       </c>
@@ -5401,12 +5305,6 @@
       <c r="F18" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G18" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H18" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K18" t="s" s="1">
         <v>86</v>
       </c>
@@ -5427,12 +5325,6 @@
       <c r="F19" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G19" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H19" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K19" t="s" s="1">
         <v>86</v>
       </c>
@@ -5453,12 +5345,6 @@
       <c r="F20" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G20" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H20" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K20" t="s" s="1">
         <v>86</v>
       </c>
@@ -5479,12 +5365,6 @@
       <c r="F21" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G21" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H21" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K21" t="s" s="1">
         <v>93</v>
       </c>
@@ -5505,12 +5385,6 @@
       <c r="F22" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G22" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H22" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K22" t="s" s="1">
         <v>93</v>
       </c>
@@ -5531,12 +5405,6 @@
       <c r="F23" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G23" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H23" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K23" t="s" s="1">
         <v>93</v>
       </c>
@@ -5557,12 +5425,6 @@
       <c r="F24" t="s" s="1">
         <v>101</v>
       </c>
-      <c r="G24" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H24" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K24" t="s" s="1">
         <v>102</v>
       </c>
@@ -5583,12 +5445,6 @@
       <c r="F25" t="s" s="1">
         <v>107</v>
       </c>
-      <c r="G25" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H25" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K25" t="s" s="1">
         <v>108</v>
       </c>
@@ -5609,12 +5465,6 @@
       <c r="F26" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G26" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H26" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K26" t="s" s="1">
         <v>112</v>
       </c>
@@ -5635,12 +5485,6 @@
       <c r="F27" t="s" s="1">
         <v>117</v>
       </c>
-      <c r="G27" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H27" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K27" t="s" s="1">
         <v>118</v>
       </c>
@@ -5661,12 +5505,6 @@
       <c r="F28" t="s" s="1">
         <v>117</v>
       </c>
-      <c r="G28" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H28" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K28" t="s" s="1">
         <v>118</v>
       </c>
@@ -5687,12 +5525,6 @@
       <c r="F29" t="s" s="1">
         <v>117</v>
       </c>
-      <c r="G29" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H29" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K29" t="s" s="1">
         <v>118</v>
       </c>
@@ -5713,12 +5545,6 @@
       <c r="F30" t="s" s="1">
         <v>127</v>
       </c>
-      <c r="G30" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H30" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K30" t="s" s="1">
         <v>128</v>
       </c>
@@ -5739,12 +5565,6 @@
       <c r="F31" t="s" s="1">
         <v>127</v>
       </c>
-      <c r="G31" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H31" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K31" t="s" s="1">
         <v>128</v>
       </c>
@@ -5765,12 +5585,6 @@
       <c r="F32" t="s" s="1">
         <v>134</v>
       </c>
-      <c r="G32" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H32" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K32" t="s" s="1">
         <v>135</v>
       </c>
@@ -5791,12 +5605,6 @@
       <c r="F33" t="s" s="1">
         <v>134</v>
       </c>
-      <c r="G33" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H33" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K33" t="s" s="1">
         <v>135</v>
       </c>
@@ -5817,12 +5625,6 @@
       <c r="F34" t="s" s="1">
         <v>101</v>
       </c>
-      <c r="G34" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H34" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K34" t="s" s="1">
         <v>141</v>
       </c>
@@ -5843,12 +5645,6 @@
       <c r="F35" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G35" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H35" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K35" t="s" s="1">
         <v>146</v>
       </c>
@@ -5869,9 +5665,6 @@
       <c r="F36" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G36" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
       <c r="H36" t="n" s="1">
         <v>0.0</v>
       </c>
@@ -5895,9 +5688,6 @@
       <c r="F37" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G37" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
       <c r="H37" t="n" s="1">
         <v>0.0</v>
       </c>
@@ -5921,9 +5711,6 @@
       <c r="F38" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G38" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
       <c r="H38" t="n" s="1">
         <v>0.0</v>
       </c>
@@ -5947,12 +5734,6 @@
       <c r="F39" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G39" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H39" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K39" t="s" s="1">
         <v>162</v>
       </c>
@@ -5973,12 +5754,6 @@
       <c r="F40" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G40" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H40" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K40" t="s" s="1">
         <v>166</v>
       </c>
@@ -5999,12 +5774,6 @@
       <c r="F41" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G41" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H41" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K41" t="s" s="1">
         <v>170</v>
       </c>
@@ -6025,12 +5794,6 @@
       <c r="F42" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G42" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H42" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K42" t="s" s="1">
         <v>174</v>
       </c>
@@ -6051,12 +5814,6 @@
       <c r="F43" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G43" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H43" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K43" t="s" s="1">
         <v>178</v>
       </c>
@@ -6077,12 +5834,6 @@
       <c r="F44" t="s" s="1">
         <v>183</v>
       </c>
-      <c r="G44" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H44" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K44" t="s" s="1">
         <v>184</v>
       </c>
@@ -6103,12 +5854,6 @@
       <c r="F45" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G45" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H45" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K45" t="s" s="1">
         <v>188</v>
       </c>
@@ -6129,12 +5874,6 @@
       <c r="F46" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G46" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H46" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K46" t="s" s="1">
         <v>192</v>
       </c>
@@ -6155,12 +5894,6 @@
       <c r="F47" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G47" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H47" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K47" t="s" s="1">
         <v>196</v>
       </c>
@@ -6181,12 +5914,6 @@
       <c r="F48" t="s" s="1">
         <v>201</v>
       </c>
-      <c r="G48" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H48" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K48" t="s" s="1">
         <v>202</v>
       </c>
@@ -6207,12 +5934,6 @@
       <c r="F49" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G49" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H49" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K49" t="s" s="1">
         <v>208</v>
       </c>
@@ -6233,12 +5954,6 @@
       <c r="F50" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G50" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H50" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K50" t="s" s="1">
         <v>212</v>
       </c>
@@ -6259,9 +5974,6 @@
       <c r="F51" t="s" s="1">
         <v>217</v>
       </c>
-      <c r="G51" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
       <c r="H51" t="n" s="1">
         <v>0.0</v>
       </c>
@@ -6285,9 +5997,6 @@
       <c r="F52" t="s" s="1">
         <v>217</v>
       </c>
-      <c r="G52" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
       <c r="H52" t="n" s="1">
         <v>0.0</v>
       </c>
@@ -6311,12 +6020,6 @@
       <c r="F53" t="s" s="1">
         <v>217</v>
       </c>
-      <c r="G53" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H53" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K53" t="s" s="1">
         <v>225</v>
       </c>
@@ -6337,12 +6040,6 @@
       <c r="F54" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G54" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H54" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K54" t="s" s="1">
         <v>230</v>
       </c>
@@ -6363,12 +6060,6 @@
       <c r="F55" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="G55" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H55" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K55" t="s" s="1">
         <v>234</v>
       </c>
@@ -6389,12 +6080,6 @@
       <c r="F56" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="G56" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H56" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K56" t="s" s="1">
         <v>234</v>
       </c>
@@ -6415,12 +6100,6 @@
       <c r="F57" t="s" s="1">
         <v>201</v>
       </c>
-      <c r="G57" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H57" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K57" t="s" s="1">
         <v>240</v>
       </c>
@@ -6441,12 +6120,6 @@
       <c r="F58" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G58" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H58" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K58" t="s" s="1">
         <v>244</v>
       </c>
@@ -6467,12 +6140,6 @@
       <c r="F59" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G59" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H59" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K59" t="s" s="1">
         <v>244</v>
       </c>
@@ -6493,12 +6160,6 @@
       <c r="F60" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G60" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H60" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K60" t="s" s="1">
         <v>244</v>
       </c>
@@ -6519,12 +6180,6 @@
       <c r="F61" t="s" s="1">
         <v>253</v>
       </c>
-      <c r="G61" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H61" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K61" t="s" s="1">
         <v>254</v>
       </c>
@@ -6545,12 +6200,6 @@
       <c r="F62" t="s" s="1">
         <v>259</v>
       </c>
-      <c r="G62" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H62" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K62" t="s" s="1">
         <v>260</v>
       </c>
@@ -6571,12 +6220,6 @@
       <c r="F63" t="s" s="1">
         <v>265</v>
       </c>
-      <c r="G63" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H63" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K63" t="s" s="1">
         <v>266</v>
       </c>
@@ -6597,12 +6240,6 @@
       <c r="F64" t="s" s="1">
         <v>271</v>
       </c>
-      <c r="G64" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H64" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K64" t="s" s="1">
         <v>272</v>
       </c>
@@ -6623,12 +6260,6 @@
       <c r="F65" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="G65" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H65" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K65" t="s" s="1">
         <v>276</v>
       </c>
@@ -6649,12 +6280,6 @@
       <c r="F66" t="s" s="1">
         <v>281</v>
       </c>
-      <c r="G66" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H66" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K66" t="s" s="1">
         <v>282</v>
       </c>
@@ -6675,12 +6300,6 @@
       <c r="F67" t="s" s="1">
         <v>287</v>
       </c>
-      <c r="G67" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H67" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K67" t="s" s="1">
         <v>288</v>
       </c>
@@ -6701,12 +6320,6 @@
       <c r="F68" t="s" s="1">
         <v>20</v>
       </c>
-      <c r="G68" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H68" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K68" t="s" s="1">
         <v>292</v>
       </c>
@@ -6727,12 +6340,6 @@
       <c r="F69" t="s" s="1">
         <v>20</v>
       </c>
-      <c r="G69" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H69" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K69" t="s" s="1">
         <v>295</v>
       </c>
@@ -6753,12 +6360,6 @@
       <c r="F70" t="s" s="1">
         <v>287</v>
       </c>
-      <c r="G70" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H70" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K70" t="s" s="1">
         <v>300</v>
       </c>
@@ -6779,12 +6380,6 @@
       <c r="F71" t="s" s="1">
         <v>305</v>
       </c>
-      <c r="G71" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H71" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K71" t="s" s="1">
         <v>306</v>
       </c>
@@ -6805,12 +6400,6 @@
       <c r="F72" t="s" s="1">
         <v>305</v>
       </c>
-      <c r="G72" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H72" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K72" t="s" s="1">
         <v>306</v>
       </c>
@@ -6828,12 +6417,6 @@
       <c r="F73" t="s" s="1">
         <v>312</v>
       </c>
-      <c r="G73" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H73" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K73" t="s" s="1">
         <v>313</v>
       </c>
@@ -6854,12 +6437,6 @@
       <c r="F74" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G74" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H74" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K74" t="s" s="1">
         <v>318</v>
       </c>
@@ -6880,12 +6457,6 @@
       <c r="F75" t="s" s="1">
         <v>323</v>
       </c>
-      <c r="G75" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H75" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K75" t="s" s="1">
         <v>324</v>
       </c>
@@ -6906,12 +6477,6 @@
       <c r="F76" t="s" s="1">
         <v>323</v>
       </c>
-      <c r="G76" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H76" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K76" t="s" s="1">
         <v>324</v>
       </c>
@@ -6932,12 +6497,6 @@
       <c r="F77" t="s" s="1">
         <v>265</v>
       </c>
-      <c r="G77" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H77" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K77" t="s" s="1">
         <v>331</v>
       </c>
@@ -6958,12 +6517,6 @@
       <c r="F78" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="G78" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H78" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K78" t="s" s="1">
         <v>27</v>
       </c>
@@ -6984,12 +6537,6 @@
       <c r="F79" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G79" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H79" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K79" t="s" s="1">
         <v>339</v>
       </c>
@@ -7010,12 +6557,6 @@
       <c r="F80" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G80" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H80" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K80" t="s" s="1">
         <v>343</v>
       </c>
@@ -7036,12 +6577,6 @@
       <c r="F81" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G81" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H81" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K81" t="s" s="1">
         <v>347</v>
       </c>
@@ -7062,12 +6597,6 @@
       <c r="F82" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G82" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H82" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K82" t="s" s="1">
         <v>244</v>
       </c>
@@ -7088,12 +6617,6 @@
       <c r="F83" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G83" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H83" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K83" t="s" s="1">
         <v>244</v>
       </c>
@@ -7114,12 +6637,6 @@
       <c r="F84" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G84" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H84" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K84" t="s" s="1">
         <v>244</v>
       </c>
@@ -7140,12 +6657,6 @@
       <c r="F85" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G85" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H85" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K85" t="s" s="1">
         <v>244</v>
       </c>
@@ -7166,12 +6677,6 @@
       <c r="F86" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G86" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H86" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K86" t="s" s="1">
         <v>244</v>
       </c>
@@ -7192,12 +6697,6 @@
       <c r="F87" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G87" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H87" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K87" t="s" s="1">
         <v>244</v>
       </c>
@@ -7218,12 +6717,6 @@
       <c r="F88" t="s" s="1">
         <v>365</v>
       </c>
-      <c r="G88" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H88" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K88" t="s" s="1">
         <v>366</v>
       </c>
@@ -7244,12 +6737,6 @@
       <c r="F89" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G89" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H89" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K89" t="s" s="1">
         <v>371</v>
       </c>
@@ -7270,12 +6757,6 @@
       <c r="F90" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G90" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H90" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K90" t="s" s="1">
         <v>371</v>
       </c>
@@ -7296,12 +6777,6 @@
       <c r="F91" t="s" s="1">
         <v>127</v>
       </c>
-      <c r="G91" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H91" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K91" t="s" s="1">
         <v>377</v>
       </c>
@@ -7322,12 +6797,6 @@
       <c r="F92" t="s" s="1">
         <v>20</v>
       </c>
-      <c r="G92" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H92" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K92" t="s" s="1">
         <v>21</v>
       </c>
@@ -7348,12 +6817,6 @@
       <c r="F93" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="G93" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H93" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K93" t="s" s="1">
         <v>384</v>
       </c>
@@ -7374,12 +6837,6 @@
       <c r="F94" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G94" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H94" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K94" t="s" s="1">
         <v>387</v>
       </c>
@@ -7400,12 +6857,6 @@
       <c r="F95" t="s" s="1">
         <v>392</v>
       </c>
-      <c r="G95" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H95" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K95" t="s" s="1">
         <v>393</v>
       </c>
@@ -7426,12 +6877,6 @@
       <c r="F96" t="s" s="1">
         <v>392</v>
       </c>
-      <c r="G96" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H96" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K96" t="s" s="1">
         <v>393</v>
       </c>
@@ -7452,12 +6897,6 @@
       <c r="F97" t="s" s="1">
         <v>400</v>
       </c>
-      <c r="G97" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H97" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K97" t="s" s="1">
         <v>401</v>
       </c>
@@ -7478,12 +6917,6 @@
       <c r="F98" t="s" s="1">
         <v>406</v>
       </c>
-      <c r="G98" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H98" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K98" t="s" s="1">
         <v>407</v>
       </c>
@@ -7504,12 +6937,6 @@
       <c r="F99" t="s" s="1">
         <v>406</v>
       </c>
-      <c r="G99" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H99" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K99" t="s" s="1">
         <v>407</v>
       </c>
@@ -7530,12 +6957,6 @@
       <c r="F100" t="s" s="1">
         <v>365</v>
       </c>
-      <c r="G100" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H100" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K100" t="s" s="1">
         <v>366</v>
       </c>
@@ -7556,12 +6977,6 @@
       <c r="F101" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G101" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H101" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K101" t="s" s="1">
         <v>244</v>
       </c>
@@ -7582,12 +6997,6 @@
       <c r="F102" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G102" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-      <c r="H102" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K102" t="s" s="1">
         <v>244</v>
       </c>
@@ -7608,12 +7017,6 @@
       <c r="F103" t="s" s="1">
         <v>421</v>
       </c>
-      <c r="G103" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H103" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K103" t="s" s="1">
         <v>422</v>
       </c>
@@ -7634,12 +7037,6 @@
       <c r="F104" t="s" s="1">
         <v>20</v>
       </c>
-      <c r="G104" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H104" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K104" t="s" s="1">
         <v>21</v>
       </c>
@@ -7660,12 +7057,6 @@
       <c r="F105" t="s" s="1">
         <v>20</v>
       </c>
-      <c r="G105" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H105" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K105" t="s" s="1">
         <v>21</v>
       </c>
@@ -7686,12 +7077,6 @@
       <c r="F106" t="s" s="1">
         <v>432</v>
       </c>
-      <c r="G106" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H106" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K106" t="s" s="1">
         <v>433</v>
       </c>
@@ -7712,12 +7097,6 @@
       <c r="F107" t="s" s="1">
         <v>438</v>
       </c>
-      <c r="G107" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H107" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K107" t="s" s="1">
         <v>439</v>
       </c>
@@ -7738,12 +7117,6 @@
       <c r="F108" t="s" s="1">
         <v>438</v>
       </c>
-      <c r="G108" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H108" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K108" t="s" s="1">
         <v>439</v>
       </c>
@@ -7764,12 +7137,6 @@
       <c r="F109" t="s" s="1">
         <v>438</v>
       </c>
-      <c r="G109" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H109" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K109" t="s" s="1">
         <v>439</v>
       </c>
@@ -7790,12 +7157,6 @@
       <c r="F110" t="s" s="1">
         <v>438</v>
       </c>
-      <c r="G110" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H110" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K110" t="s" s="1">
         <v>439</v>
       </c>
@@ -7816,12 +7177,6 @@
       <c r="F111" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G111" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H111" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K111" t="s" s="1">
         <v>439</v>
       </c>
@@ -7842,12 +7197,6 @@
       <c r="F112" t="s" s="1">
         <v>438</v>
       </c>
-      <c r="G112" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H112" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K112" t="s" s="1">
         <v>439</v>
       </c>
@@ -7868,12 +7217,6 @@
       <c r="F113" t="s" s="1">
         <v>438</v>
       </c>
-      <c r="G113" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H113" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K113" t="s" s="1">
         <v>439</v>
       </c>
@@ -7894,12 +7237,6 @@
       <c r="F114" t="s" s="1">
         <v>438</v>
       </c>
-      <c r="G114" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H114" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K114" t="s" s="1">
         <v>439</v>
       </c>
@@ -7920,12 +7257,6 @@
       <c r="F115" t="s" s="1">
         <v>20</v>
       </c>
-      <c r="G115" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H115" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K115" t="s" s="1">
         <v>458</v>
       </c>
@@ -7946,12 +7277,6 @@
       <c r="F116" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G116" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H116" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K116" t="s" s="1">
         <v>463</v>
       </c>
@@ -7972,12 +7297,6 @@
       <c r="F117" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="G117" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H117" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K117" t="s" s="1">
         <v>463</v>
       </c>
@@ -7998,12 +7317,6 @@
       <c r="F118" t="s" s="1">
         <v>127</v>
       </c>
-      <c r="G118" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H118" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K118" t="s" s="1">
         <v>469</v>
       </c>
@@ -8024,12 +7337,6 @@
       <c r="F119" t="s" s="1">
         <v>265</v>
       </c>
-      <c r="G119" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H119" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K119" t="s" s="1">
         <v>474</v>
       </c>
@@ -8050,12 +7357,6 @@
       <c r="F120" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G120" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H120" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K120" t="s" s="1">
         <v>387</v>
       </c>
@@ -8076,12 +7377,6 @@
       <c r="F121" t="s" s="1">
         <v>207</v>
       </c>
-      <c r="G121" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H121" t="n" s="1">
-        <v>1000.0</v>
-      </c>
       <c r="K121" t="s" s="1">
         <v>387</v>
       </c>
@@ -8101,12 +7396,6 @@
       </c>
       <c r="F122" t="s" s="1">
         <v>207</v>
-      </c>
-      <c r="G122" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H122" t="n" s="1">
-        <v>1000.0</v>
       </c>
       <c r="K122" t="s" s="1">
         <v>387</v>
@@ -13831,6 +13120,12 @@
       <c r="C2" t="s" s="9">
         <v>1600</v>
       </c>
+      <c r="E2" t="n" s="9">
+        <v>-1000.0</v>
+      </c>
+      <c r="F2" t="n" s="9">
+        <v>1000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
